--- a/inventory.xlsx
+++ b/inventory.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30317"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://atio365gov-my.sharepoint.us/personal/ezxlz1_alsn_com/Documents/Python Scripts/eKanBan Scheduling/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ezxlz1\Downloads\ATI-Grocery-List-main\ATI-Grocery-List-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="8_{0CCED1C5-6AD0-4945-B7AC-C1491C4F0792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D1CA1935-BC2B-408E-9484-487A31F00C06}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C306D10F-D52A-4E3F-A89F-D1F05D0F7F94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A4C69D7D-69AF-42A9-AF5F-55EF7AC85EA8}"/>
   </bookViews>
@@ -384,7 +384,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -973,9 +973,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA6FEA44-EBB9-4EE9-BDF5-F029CB329C85}">
   <dimension ref="A1:S36"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:19" ht="75.75" thickBot="1">
+    <row r="1" spans="1:19" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1034,7 +1034,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="15.75" thickBot="1">
+    <row r="2" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6">
         <v>50036</v>
       </c>
@@ -1096,7 +1096,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="15.75" thickBot="1">
+    <row r="3" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6">
         <v>50257</v>
       </c>
@@ -1157,7 +1157,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="15.75" thickBot="1">
+    <row r="4" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="14">
         <v>50258</v>
       </c>
@@ -1219,7 +1219,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="15.75" thickBot="1">
+    <row r="5" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="6">
         <v>50259</v>
       </c>
@@ -1280,7 +1280,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="15.75" thickBot="1">
+    <row r="6" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="14">
         <v>50260</v>
       </c>
@@ -1341,7 +1341,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="15.75" thickBot="1">
+    <row r="7" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
         <v>50261</v>
       </c>
@@ -1403,7 +1403,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="15.75" thickBot="1">
+    <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="14">
         <v>50262</v>
       </c>
@@ -1465,7 +1465,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="15.75" thickBot="1">
+    <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
         <v>50263</v>
       </c>
@@ -1526,7 +1526,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="15.75" thickBot="1">
+    <row r="10" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
         <v>50267</v>
       </c>
@@ -1588,7 +1588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="15.75" thickBot="1">
+    <row r="11" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="14">
         <v>29505699</v>
       </c>
@@ -1630,8 +1630,7 @@
         <v>14</v>
       </c>
       <c r="O11" s="9">
-        <f t="shared" si="2"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P11" s="17">
         <v>3</v>
@@ -1648,7 +1647,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="15.75" thickBot="1">
+    <row r="12" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="6">
         <v>50268</v>
       </c>
@@ -1710,7 +1709,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="15.75" thickBot="1">
+    <row r="13" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6">
         <v>50276</v>
       </c>
@@ -1771,7 +1770,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="15.75" thickBot="1">
+    <row r="14" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="6">
         <v>50283</v>
       </c>
@@ -1832,7 +1831,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:19" ht="15.75" thickBot="1">
+    <row r="15" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="14">
         <v>29537246</v>
       </c>
@@ -1876,8 +1875,7 @@
         <v>16</v>
       </c>
       <c r="O15" s="9">
-        <f t="shared" ref="O15:O26" si="3">ROUNDUP(M15/J15,0)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P15" s="17">
         <v>9</v>
@@ -1894,7 +1892,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:19" ht="15.75" thickBot="1">
+    <row r="16" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="14">
         <v>29542518</v>
       </c>
@@ -1936,7 +1934,7 @@
         <v>16</v>
       </c>
       <c r="O16" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P16" s="17">
         <v>6</v>
@@ -1953,7 +1951,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:19" ht="15.75" thickBot="1">
+    <row r="17" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="6">
         <v>29547912</v>
       </c>
@@ -1995,8 +1993,7 @@
         <v>16</v>
       </c>
       <c r="O17" s="9">
-        <f t="shared" si="3"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P17" s="17">
         <v>11</v>
@@ -2013,7 +2010,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:19" ht="15.75" thickBot="1">
+    <row r="18" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="6">
         <v>29541112</v>
       </c>
@@ -2057,8 +2054,7 @@
         <v>16</v>
       </c>
       <c r="O18" s="9">
-        <f t="shared" si="3"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P18" s="17">
         <v>13</v>
@@ -2075,7 +2071,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="19" spans="1:19" ht="15.75" thickBot="1">
+    <row r="19" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="14">
         <v>29544957</v>
       </c>
@@ -2117,8 +2113,7 @@
         <v>15</v>
       </c>
       <c r="O19" s="9">
-        <f t="shared" si="3"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P19" s="17">
         <v>13</v>
@@ -2135,7 +2130,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="20" spans="1:19" ht="15.75" thickBot="1">
+    <row r="20" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6">
         <v>29540181</v>
       </c>
@@ -2177,8 +2172,7 @@
         <v>16</v>
       </c>
       <c r="O20" s="9">
-        <f t="shared" si="3"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P20" s="17">
         <v>3</v>
@@ -2188,14 +2182,14 @@
       </c>
       <c r="R20" s="11">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20" s="12">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="1:19" ht="15.75" thickBot="1">
+    <row r="21" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="14">
         <v>29540134</v>
       </c>
@@ -2239,8 +2233,7 @@
         <v>15</v>
       </c>
       <c r="O21" s="9">
-        <f t="shared" si="3"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P21" s="17">
         <v>1</v>
@@ -2250,14 +2243,14 @@
       </c>
       <c r="R21" s="11">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S21" s="12">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:19" ht="15.75" thickBot="1">
+    <row r="22" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="6">
         <v>29540140</v>
       </c>
@@ -2299,8 +2292,7 @@
         <v>15</v>
       </c>
       <c r="O22" s="9">
-        <f t="shared" si="3"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P22" s="17">
         <v>6</v>
@@ -2317,7 +2309,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:19" ht="15.75" thickBot="1">
+    <row r="23" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="14">
         <v>29555865</v>
       </c>
@@ -2359,8 +2351,7 @@
         <v>5</v>
       </c>
       <c r="O23" s="9">
-        <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P23" s="17">
         <v>7</v>
@@ -2377,7 +2368,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:19" ht="15.75" thickBot="1">
+    <row r="24" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="14">
         <v>29549766</v>
       </c>
@@ -2419,8 +2410,7 @@
         <v>14</v>
       </c>
       <c r="O24" s="9">
-        <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P24" s="17">
         <v>13</v>
@@ -2437,7 +2427,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="25" spans="1:19" ht="15.75" thickBot="1">
+    <row r="25" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="6">
         <v>29530484</v>
       </c>
@@ -2479,7 +2469,7 @@
         <v>14</v>
       </c>
       <c r="O25" s="9">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P25" s="17">
         <v>6</v>
@@ -2496,7 +2486,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:19" ht="15.75" thickBot="1">
+    <row r="26" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="6">
         <v>29515650</v>
       </c>
@@ -2538,8 +2528,7 @@
         <v>14</v>
       </c>
       <c r="O26" s="9">
-        <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P26" s="17">
         <v>2</v>
@@ -2556,7 +2545,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="1:19" ht="15.75" thickBot="1">
+    <row r="27" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="14">
         <v>29534507</v>
       </c>
@@ -2598,7 +2587,7 @@
         <v>13</v>
       </c>
       <c r="O27" s="9">
-        <f t="shared" ref="O27:O36" si="4">ROUNDUP((M27*2)/J27,0)</f>
+        <f t="shared" ref="O27:O36" si="3">ROUNDUP((M27*2)/J27,0)</f>
         <v>3</v>
       </c>
       <c r="P27" s="10">
@@ -2616,7 +2605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:19" ht="15.75" thickBot="1">
+    <row r="28" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6">
         <v>29556983</v>
       </c>
@@ -2660,7 +2649,7 @@
         <v>73</v>
       </c>
       <c r="O28" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="P28" s="10">
@@ -2678,7 +2667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:19" ht="15.75" thickBot="1">
+    <row r="29" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="14">
         <v>29556986</v>
       </c>
@@ -2722,7 +2711,7 @@
         <v>58</v>
       </c>
       <c r="O29" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="P29" s="10">
@@ -2740,7 +2729,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:19" ht="15.75" thickBot="1">
+    <row r="30" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="6">
         <v>29556987</v>
       </c>
@@ -2784,7 +2773,7 @@
         <v>46</v>
       </c>
       <c r="O30" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="P30" s="10">
@@ -2802,7 +2791,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:19" ht="15.75" thickBot="1">
+    <row r="31" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="14">
         <v>29556988</v>
       </c>
@@ -2846,7 +2835,7 @@
         <v>53</v>
       </c>
       <c r="O31" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="P31" s="10">
@@ -2864,7 +2853,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:19" ht="15.75" thickBot="1">
+    <row r="32" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="6">
         <v>29556989</v>
       </c>
@@ -2925,7 +2914,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:19" ht="15.75" thickBot="1">
+    <row r="33" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="14">
         <v>29556990</v>
       </c>
@@ -2986,7 +2975,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:19" ht="15.75" thickBot="1">
+    <row r="34" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="6">
         <v>29556991</v>
       </c>
@@ -3030,7 +3019,7 @@
         <v>53</v>
       </c>
       <c r="O34" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="P34" s="10">
@@ -3048,7 +3037,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:19" ht="15.75" thickBot="1">
+    <row r="35" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="14">
         <v>29556992</v>
       </c>
@@ -3109,7 +3098,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:19" ht="15.75" thickBot="1">
+    <row r="36" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="6">
         <v>29556993</v>
       </c>
@@ -3153,7 +3142,7 @@
         <v>17</v>
       </c>
       <c r="O36" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="P36" s="10">
